--- a/temp/contactData (8).xlsx
+++ b/temp/contactData (8).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7050"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="AddressBook" sheetId="1" r:id="rId1"/>
@@ -65,28 +65,28 @@
     <t>PUBLIC</t>
   </si>
   <si>
-    <t>IS_EXCEL</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>Moithu</t>
-  </si>
-  <si>
-    <t>kr</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Kottayam</t>
-  </si>
-  <si>
-    <t>kayamkulam</t>
-  </si>
-  <si>
-    <t>reading,writing</t>
+    <t>Jagan</t>
+  </si>
+  <si>
+    <t>Nadh</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>jagan@gmail.com</t>
+  </si>
+  <si>
+    <t>porbandhar</t>
+  </si>
+  <si>
+    <t>gujarat</t>
+  </si>
+  <si>
+    <t>travelling,reading</t>
   </si>
 </sst>
 </file>
@@ -116,18 +116,18 @@
       <charset val="0"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -575,31 +575,31 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -723,12 +723,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1264,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="4" width="25" customWidth="1"/>
@@ -1274,10 +1277,11 @@
     <col min="9" max="9" width="25" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="50" customWidth="1"/>
-    <col min="12" max="14" width="20" customWidth="1"/>
+    <col min="12" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1314,28 +1318,28 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2">
+        <v>36852</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2">
-        <v>43851</v>
-      </c>
       <c r="G2">
-        <v>9898989898</v>
+        <v>9898989800</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -1344,19 +1348,19 @@
         <v>18</v>
       </c>
       <c r="J2">
-        <v>684213</v>
+        <v>689789</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="jagan@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
